--- a/JO11-1/JO11-1_matchesDB.xlsx
+++ b/JO11-1/JO11-1_matchesDB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLTSWIERZE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76CAB4FD-9A35-4EF7-BECF-1F51EA6D17A3}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchesDB" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="65">
   <si>
     <t>Matches</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t>Biesbosch 39, 1115 HE Duivendrecht</t>
+  </si>
+  <si>
+    <t>Escapade 5, 1183 NM Amstelveen</t>
+  </si>
+  <si>
+    <t>1,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,0,0</t>
   </si>
 </sst>
 </file>
@@ -554,14 +563,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,7 +805,7 @@
       </c>
       <c r="B1" s="5">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="7">
@@ -872,7 +881,7 @@
       </c>
       <c r="B3" s="10">
         <f>COUNTIF(J11:J40,"L")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -983,7 +992,7 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1020,7 +1029,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1057,7 +1066,7 @@
       </c>
       <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1302,7 +1311,7 @@
         <v>32</v>
       </c>
       <c r="J12" s="17" t="str">
-        <f t="shared" ref="J11:J40" si="1">IF(AND(NOT(ISBLANK(K12)),NOT(ISBLANK(L12))),IF(K12&gt;L12,"W",IF(K12&lt;L12,"L","D")),"")</f>
+        <f t="shared" ref="J12:J13" si="1">IF(AND(NOT(ISBLANK(K12)),NOT(ISBLANK(L12))),IF(K12&gt;L12,"W",IF(K12&lt;L12,"L","D")),"")</f>
         <v>W</v>
       </c>
       <c r="K12" s="24" cm="1">
@@ -1526,10 +1535,10 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F15" s="18"/>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="29" t="s">
         <v>61</v>
       </c>
       <c r="I15" s="18" t="s">
@@ -1537,28 +1546,52 @@
       </c>
       <c r="J15" s="17" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K15" s="24" t="str">
+        <v>L</v>
+      </c>
+      <c r="K15" s="24">
         <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:X15,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L15" s="18"/>
-      <c r="M15" s="24" t="str">
+        <v>2</v>
+      </c>
+      <c r="L15" s="18">
+        <v>7</v>
+      </c>
+      <c r="M15" s="24">
         <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:X15,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="W15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X15" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="Y15" s="6"/>
       <c r="AD15" s="6"/>
     </row>
@@ -1577,13 +1610,15 @@
         <v>46277</v>
       </c>
       <c r="E16" s="21">
-        <v>0.44791666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="F16" s="18"/>
       <c r="G16" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="18"/>
+      <c r="H16" s="18" t="s">
+        <v>62</v>
+      </c>
       <c r="I16" s="18" t="s">
         <v>37</v>
       </c>
@@ -2780,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6">
         <v>1</v>
@@ -2797,7 +2832,7 @@
       <c r="M45" s="6"/>
       <c r="N45" s="27">
         <f t="shared" ref="N45:N48" si="4">SUM(B45:M45)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
@@ -2834,13 +2869,13 @@
         <v>1</v>
       </c>
       <c r="H46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="6">
         <v>1</v>
       </c>
       <c r="J46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6">
         <v>0</v>
@@ -2873,13 +2908,13 @@
         <v>0</v>
       </c>
       <c r="C47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" s="6">
         <v>0</v>
       </c>
       <c r="E47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6">
         <v>0</v>
@@ -2905,7 +2940,7 @@
       <c r="M47" s="6"/>
       <c r="N47" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -2930,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6">
         <v>0</v>
@@ -2942,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="6">
         <v>0</v>
@@ -2959,7 +2994,7 @@
       <c r="M48" s="6"/>
       <c r="N48" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
@@ -2981,15 +3016,15 @@
       </c>
       <c r="C49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="D49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="E49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="F49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3001,7 +3036,7 @@
       </c>
       <c r="H49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0,0,0,0</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="I49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3009,7 +3044,7 @@
       </c>
       <c r="J49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="K49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3170,13 +3205,13 @@
         <v>49</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>49</v>
@@ -3185,13 +3220,13 @@
         <v>49</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>49</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>48</v>
@@ -33121,7 +33156,7 @@
   <dimension ref="A1:T47"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
@@ -33163,8 +33198,8 @@
       <c r="S1" s="6"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -33172,39 +33207,39 @@
       </c>
       <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="11">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="11">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="11">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="11">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="11">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="11">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="11">
         <f t="array" ref="L2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
@@ -33219,14 +33254,14 @@
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="29"/>
+    <row r="3" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A3" s="31"/>
       <c r="B3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="23">
         <f>C2/MatchesDB!$B$1</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3" s="23">
         <f>D2/MatchesDB!$B$1</f>
@@ -33250,11 +33285,11 @@
       </c>
       <c r="I3" s="23">
         <f>I2/MatchesDB!$B$1</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="23" t="e">
+        <v>0.2</v>
+      </c>
+      <c r="J3" s="23">
         <f>J2/(MatchesDB!$B$1-4)</f>
-        <v>#DIV/0!</v>
+        <v>5</v>
       </c>
       <c r="K3" s="23">
         <f>K2/MatchesDB!$B$1</f>
@@ -33262,7 +33297,7 @@
       </c>
       <c r="L3" s="23">
         <f>L2/MatchesDB!$B$1</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -33273,8 +33308,8 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -33282,35 +33317,35 @@
       </c>
       <c r="C4" s="25">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="25">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="25">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="25">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="25">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="25">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="25">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="25">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="25">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33329,8 +33364,8 @@
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="29"/>
+    <row r="5" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
       <c r="B5" s="4" t="s">
         <v>33</v>
       </c>
@@ -33358,9 +33393,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I5" s="23" t="e">
+      <c r="I5" s="23">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="J5" s="23">
         <f t="shared" si="0"/>
@@ -33368,7 +33403,7 @@
       </c>
       <c r="K5" s="23">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="23">
         <f t="shared" si="0"/>
@@ -33383,8 +33418,8 @@
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -33396,7 +33431,7 @@
       </c>
       <c r="D6" s="11" cm="1">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="11">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33404,7 +33439,7 @@
       </c>
       <c r="F6" s="11">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="11">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33439,8 +33474,8 @@
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="29"/>
+    <row r="7" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
       <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
@@ -33450,35 +33485,35 @@
       </c>
       <c r="D7" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E7" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F7" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G7" s="26">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I7" s="26" t="e">
+      <c r="I7" s="26">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J7" s="26">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="K7" s="26">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L7" s="26">
         <f t="shared" si="1"/>
@@ -33493,8 +33528,8 @@
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A8" s="30" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -33510,7 +33545,7 @@
       </c>
       <c r="E8" s="25">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="25">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33526,7 +33561,7 @@
       </c>
       <c r="I8" s="25">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="25">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33549,8 +33584,8 @@
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="29"/>
+    <row r="9" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A9" s="31"/>
       <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
@@ -33564,7 +33599,7 @@
       </c>
       <c r="E9" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="26">
         <f t="shared" si="2"/>
@@ -33578,9 +33613,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="26" t="e">
+      <c r="I9" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="J9" s="26">
         <f t="shared" si="2"/>
@@ -33603,8 +33638,8 @@
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -33616,15 +33651,15 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="11">
         <f t="shared" si="3"/>
@@ -33636,7 +33671,7 @@
       </c>
       <c r="I10" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="11">
         <f t="shared" si="3"/>
@@ -33659,8 +33694,8 @@
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="29"/>
+    <row r="11" spans="1:20" ht="14" x14ac:dyDescent="0.3">
+      <c r="A11" s="31"/>
       <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
@@ -33670,35 +33705,35 @@
       </c>
       <c r="D11" s="26">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E11" s="26">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F11" s="26">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="26">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I11" s="26" t="e">
+      <c r="I11" s="26">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="J11" s="26">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="K11" s="26">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" si="4"/>

--- a/JO11-1/JO11-1_matchesDB.xlsx
+++ b/JO11-1/JO11-1_matchesDB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/Misc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/PRV/RKAVIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76CAB4FD-9A35-4EF7-BECF-1F51EA6D17A3}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80535FEB-1D3D-41D8-8882-ADFAFAEF6540}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11130" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchesDB" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="70">
   <si>
     <t>Matches</t>
   </si>
@@ -184,12 +184,6 @@
     <t>Goal contribution</t>
   </si>
   <si>
-    <t>Player2</t>
-  </si>
-  <si>
-    <t>Player3</t>
-  </si>
-  <si>
     <t>showup</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
   </si>
   <si>
     <t>Maddox</t>
-  </si>
-  <si>
-    <t>,,,</t>
   </si>
   <si>
     <t>0,0,0,0</t>
@@ -255,6 +246,30 @@
   <si>
     <t>1,0,0,0</t>
   </si>
+  <si>
+    <t>Kay</t>
+  </si>
+  <si>
+    <t>Noam</t>
+  </si>
+  <si>
+    <t>Oefenen</t>
+  </si>
+  <si>
+    <t>1,1,4,1</t>
+  </si>
+  <si>
+    <t>1,1,0,2</t>
+  </si>
+  <si>
+    <t>1,1,1,4</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>Gustav Mahlerlaan 2009, 1081 LB Amsterdam</t>
+  </si>
 </sst>
 </file>
 
@@ -274,48 +289,57 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -805,7 +829,7 @@
       </c>
       <c r="B1" s="5">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="7">
@@ -844,7 +868,7 @@
       </c>
       <c r="B2" s="10">
         <f>COUNTIF(J11:J40,"W")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -955,7 +979,7 @@
       </c>
       <c r="B5" s="10">
         <f>B2*3+B4</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -992,7 +1016,7 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1029,7 +1053,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1066,7 +1090,7 @@
       </c>
       <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1197,12 +1221,14 @@
         <v>9</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y10" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="Y10" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="AD10" s="6"/>
     </row>
     <row r="11" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1224,7 +1250,7 @@
       </c>
       <c r="F11" s="22"/>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>31</v>
@@ -1237,50 +1263,52 @@
         <v>D</v>
       </c>
       <c r="K11" s="24" cm="1">
-        <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:X11,5,1)*1), "")</f>
+        <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:Y11,5,1)*1), "")</f>
         <v>0</v>
       </c>
       <c r="L11" s="18">
         <v>0</v>
       </c>
-      <c r="M11" s="24">
-        <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:X11,1)*1), "")</f>
+      <c r="M11" s="24" cm="1">
+        <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:Y11,1)*1), "")</f>
         <v>8</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y11" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="Y11" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="AD11" s="6"/>
     </row>
     <row r="12" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1302,7 +1330,7 @@
       </c>
       <c r="F12" s="22"/>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>31</v>
@@ -1315,50 +1343,52 @@
         <v>W</v>
       </c>
       <c r="K12" s="24" cm="1">
-        <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:X12,5,1)*1), "")</f>
+        <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:Y12,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L12" s="18">
         <v>0</v>
       </c>
-      <c r="M12" s="24">
-        <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:X12,1)*1), "")</f>
+      <c r="M12" s="24" cm="1">
+        <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:Y12,1)*1), "")</f>
         <v>8</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="U12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="W12" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="X12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y12" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="Y12" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="AD12" s="6"/>
     </row>
     <row r="13" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1380,7 +1410,7 @@
       </c>
       <c r="F13" s="22"/>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>31</v>
@@ -1392,51 +1422,53 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K13" s="24">
-        <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:X13,5,1)*1), "")</f>
+      <c r="K13" s="24" cm="1">
+        <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:Y13,5,1)*1), "")</f>
         <v>8</v>
       </c>
       <c r="L13" s="18">
         <v>0</v>
       </c>
-      <c r="M13" s="24">
-        <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:X13,1)*1), "")</f>
+      <c r="M13" s="24" cm="1">
+        <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:Y13,1)*1), "")</f>
         <v>8</v>
       </c>
       <c r="N13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="P13" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="U13" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="V13" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="X13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y13" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="X13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y13" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="AD13" s="6"/>
     </row>
     <row r="14" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1458,7 +1490,7 @@
       </c>
       <c r="F14" s="22"/>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>31</v>
@@ -1470,54 +1502,56 @@
         <f t="shared" ref="J14:J40" si="2">IF(AND(NOT(ISBLANK(K14)),NOT(ISBLANK(L14))),IF(K14&gt;L14,"W",IF(K14&lt;L14,"L","D")),"")</f>
         <v>L</v>
       </c>
-      <c r="K14" s="24">
-        <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:X14,5,1)*1), "")</f>
+      <c r="K14" s="24" cm="1">
+        <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:Y14,5,1)*1), "")</f>
         <v>0</v>
       </c>
       <c r="L14" s="18">
         <v>1</v>
       </c>
-      <c r="M14" s="24">
-        <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:X14,1)*1), "")</f>
+      <c r="M14" s="24" cm="1">
+        <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:Y14,1)*1), "")</f>
         <v>8</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="X14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y14" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="X14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y14" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="AD14" s="6"/>
     </row>
-    <row r="15" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1536,10 +1570,10 @@
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>32</v>
@@ -1548,51 +1582,53 @@
         <f t="shared" si="2"/>
         <v>L</v>
       </c>
-      <c r="K15" s="24">
-        <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:X15,5,1)*1), "")</f>
+      <c r="K15" s="24" cm="1">
+        <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:Y15,5,1)*1), "")</f>
         <v>2</v>
       </c>
       <c r="L15" s="18">
         <v>7</v>
       </c>
-      <c r="M15" s="24">
-        <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:X15,1)*1), "")</f>
+      <c r="M15" s="24" cm="1">
+        <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:Y15,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y15" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="Y15" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="AD15" s="6"/>
     </row>
     <row r="16" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1603,8 +1639,8 @@
       <c r="B16" s="18">
         <v>1</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>36</v>
+      <c r="C16" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D16" s="20">
         <v>46277</v>
@@ -1614,39 +1650,65 @@
       </c>
       <c r="F16" s="18"/>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>37</v>
       </c>
       <c r="J16" s="17" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K16" s="24" t="str">
-        <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:X16,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="24" t="str">
-        <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:X16,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
+        <v>W</v>
+      </c>
+      <c r="K16" s="24" cm="1">
+        <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:Y16,5,1)*1), "")</f>
+        <v>10</v>
+      </c>
+      <c r="L16" s="18">
+        <v>3</v>
+      </c>
+      <c r="M16" s="24" cm="1">
+        <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:Y16,1)*1), "")</f>
+        <v>9</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="W16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y16" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="AD16" s="6"/>
     </row>
     <row r="17" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1668,9 +1730,11 @@
       </c>
       <c r="F17" s="18"/>
       <c r="G17" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="18"/>
+        <v>55</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>69</v>
+      </c>
       <c r="I17" s="18" t="s">
         <v>32</v>
       </c>
@@ -1678,13 +1742,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K17" s="24" t="str">
-        <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:X17,5,1)*1), "")</f>
+      <c r="K17" s="24" t="str" cm="1">
+        <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:Y17,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L17" s="18"/>
-      <c r="M17" s="24" t="str">
-        <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:X17,1)*1), "")</f>
+      <c r="M17" s="24" t="str" cm="1">
+        <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:Y17,1)*1), "")</f>
         <v/>
       </c>
       <c r="N17" s="8"/>
@@ -1697,8 +1761,8 @@
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
       <c r="AD17" s="6"/>
     </row>
     <row r="18" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1716,13 +1780,15 @@
         <v>46291</v>
       </c>
       <c r="E18" s="21">
-        <v>0.44791666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="18"/>
       <c r="I18" s="18" t="s">
         <v>37</v>
       </c>
@@ -1730,13 +1796,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K18" s="24" t="str">
-        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:X18,5,1)*1), "")</f>
+      <c r="K18" s="24" t="str" cm="1">
+        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:Y18,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L18" s="18"/>
-      <c r="M18" s="24" t="str">
-        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:X18,1)*1), "")</f>
+      <c r="M18" s="24" t="str" cm="1">
+        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
         <v/>
       </c>
       <c r="N18" s="8"/>
@@ -1749,8 +1815,8 @@
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
       <c r="AD18" s="6"/>
     </row>
     <row r="19" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1768,13 +1834,15 @@
         <v>46298</v>
       </c>
       <c r="E19" s="21">
-        <v>0.44791666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="18"/>
+        <v>57</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>59</v>
+      </c>
       <c r="I19" s="18" t="s">
         <v>37</v>
       </c>
@@ -1782,13 +1850,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K19" s="24" t="str">
-        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:X19,5,1)*1), "")</f>
+      <c r="K19" s="24" t="str" cm="1">
+        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L19" s="18"/>
-      <c r="M19" s="24" t="str">
-        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:X19,1)*1), "")</f>
+      <c r="M19" s="24" t="str" cm="1">
+        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
         <v/>
       </c>
       <c r="N19" s="8"/>
@@ -1801,8 +1869,8 @@
       <c r="U19" s="8"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
       <c r="AD19" s="6"/>
     </row>
     <row r="20" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1822,13 +1890,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K20" s="24" t="str">
-        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:X20,5,1)*1), "")</f>
+      <c r="K20" s="24" t="str" cm="1">
+        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:Y20,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L20" s="18"/>
-      <c r="M20" s="24" t="str">
-        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:X20,1)*1), "")</f>
+      <c r="M20" s="24" t="str" cm="1">
+        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
         <v/>
       </c>
       <c r="N20" s="8"/>
@@ -1841,8 +1909,8 @@
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="8"/>
       <c r="AD20" s="6"/>
     </row>
     <row r="21" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1862,13 +1930,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K21" s="24" t="str">
-        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:X21,5,1)*1), "")</f>
+      <c r="K21" s="24" t="str" cm="1">
+        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:Y21,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L21" s="18"/>
-      <c r="M21" s="24" t="str">
-        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:X21,1)*1), "")</f>
+      <c r="M21" s="24" t="str" cm="1">
+        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
         <v/>
       </c>
       <c r="N21" s="8"/>
@@ -1881,8 +1949,8 @@
       <c r="U21" s="8"/>
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8"/>
       <c r="AD21" s="6"/>
     </row>
     <row r="22" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1902,13 +1970,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K22" s="24" t="str">
-        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:X22,5,1)*1), "")</f>
+      <c r="K22" s="24" t="str" cm="1">
+        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:Y22,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L22" s="18"/>
-      <c r="M22" s="24" t="str">
-        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:X22,1)*1), "")</f>
+      <c r="M22" s="24" t="str" cm="1">
+        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
         <v/>
       </c>
       <c r="N22" s="8"/>
@@ -1921,8 +1989,8 @@
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8"/>
       <c r="AD22" s="6"/>
     </row>
     <row r="23" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1942,13 +2010,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K23" s="24" t="str">
-        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:X23,5,1)*1), "")</f>
+      <c r="K23" s="24" t="str" cm="1">
+        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:Y23,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L23" s="18"/>
-      <c r="M23" s="24" t="str">
-        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:X23,1)*1), "")</f>
+      <c r="M23" s="24" t="str" cm="1">
+        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
         <v/>
       </c>
       <c r="N23" s="8"/>
@@ -1961,8 +2029,8 @@
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="8"/>
       <c r="AD23" s="6"/>
     </row>
     <row r="24" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1982,13 +2050,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K24" s="24" t="str">
-        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:X24,5,1)*1), "")</f>
+      <c r="K24" s="24" t="str" cm="1">
+        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:Y24,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L24" s="18"/>
-      <c r="M24" s="24" t="str">
-        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:X24,1)*1), "")</f>
+      <c r="M24" s="24" t="str" cm="1">
+        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
         <v/>
       </c>
       <c r="N24" s="8"/>
@@ -2001,8 +2069,8 @@
       <c r="U24" s="8"/>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="8"/>
       <c r="AD24" s="6"/>
     </row>
     <row r="25" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2022,13 +2090,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K25" s="24" t="str">
-        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:X25,5,1)*1), "")</f>
+      <c r="K25" s="24" t="str" cm="1">
+        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:Y25,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L25" s="18"/>
-      <c r="M25" s="24" t="str">
-        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:X25,1)*1), "")</f>
+      <c r="M25" s="24" t="str" cm="1">
+        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
         <v/>
       </c>
       <c r="N25" s="8"/>
@@ -2041,8 +2109,8 @@
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
       <c r="AD25" s="6"/>
     </row>
     <row r="26" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2062,13 +2130,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K26" s="24" t="str">
-        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:X26,5,1)*1), "")</f>
+      <c r="K26" s="24" t="str" cm="1">
+        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L26" s="18"/>
-      <c r="M26" s="24" t="str">
-        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:X26,1)*1), "")</f>
+      <c r="M26" s="24" t="str" cm="1">
+        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
         <v/>
       </c>
       <c r="N26" s="8"/>
@@ -2081,8 +2149,8 @@
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
       <c r="AD26" s="6"/>
     </row>
     <row r="27" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2102,13 +2170,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K27" s="24" t="str">
-        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:X27,5,1)*1), "")</f>
+      <c r="K27" s="24" t="str" cm="1">
+        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:Y27,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L27" s="18"/>
-      <c r="M27" s="24" t="str">
-        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:X27,1)*1), "")</f>
+      <c r="M27" s="24" t="str" cm="1">
+        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:Y27,1)*1), "")</f>
         <v/>
       </c>
       <c r="N27" s="8"/>
@@ -2121,8 +2189,8 @@
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="6"/>
+      <c r="X27" s="8"/>
+      <c r="Y27" s="8"/>
       <c r="AD27" s="6"/>
     </row>
     <row r="28" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2142,13 +2210,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K28" s="24" t="str">
-        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:X28,5,1)*1), "")</f>
+      <c r="K28" s="24" t="str" cm="1">
+        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:Y28,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L28" s="18"/>
-      <c r="M28" s="24" t="str">
-        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:X28,1)*1), "")</f>
+      <c r="M28" s="24" t="str" cm="1">
+        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:Y28,1)*1), "")</f>
         <v/>
       </c>
       <c r="N28" s="8"/>
@@ -2161,8 +2229,8 @@
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
       <c r="AD28" s="6"/>
     </row>
     <row r="29" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2182,13 +2250,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K29" s="24" t="str">
-        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:X29,5,1)*1), "")</f>
+      <c r="K29" s="24" t="str" cm="1">
+        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:Y29,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L29" s="18"/>
-      <c r="M29" s="24" t="str">
-        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:X29,1)*1), "")</f>
+      <c r="M29" s="24" t="str" cm="1">
+        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:Y29,1)*1), "")</f>
         <v/>
       </c>
       <c r="N29" s="8"/>
@@ -2201,8 +2269,8 @@
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8"/>
       <c r="AD29" s="6"/>
     </row>
     <row r="30" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2222,13 +2290,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K30" s="24" t="str">
-        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:X30,5,1)*1), "")</f>
+      <c r="K30" s="24" t="str" cm="1">
+        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:Y30,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L30" s="18"/>
-      <c r="M30" s="24" t="str">
-        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:X30,1)*1), "")</f>
+      <c r="M30" s="24" t="str" cm="1">
+        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:Y30,1)*1), "")</f>
         <v/>
       </c>
       <c r="N30" s="8"/>
@@ -2241,8 +2309,8 @@
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8"/>
       <c r="AD30" s="6"/>
     </row>
     <row r="31" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2262,13 +2330,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K31" s="24" t="str">
-        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:X31,5,1)*1), "")</f>
+      <c r="K31" s="24" t="str" cm="1">
+        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:Y31,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L31" s="18"/>
-      <c r="M31" s="24" t="str">
-        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:X31,1)*1), "")</f>
+      <c r="M31" s="24" t="str" cm="1">
+        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:Y31,1)*1), "")</f>
         <v/>
       </c>
       <c r="N31" s="8"/>
@@ -2281,8 +2349,8 @@
       <c r="U31" s="8"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
       <c r="AD31" s="6"/>
     </row>
     <row r="32" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2302,13 +2370,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K32" s="24" t="str">
-        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:X32,5,1)*1), "")</f>
+      <c r="K32" s="24" t="str" cm="1">
+        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:Y32,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L32" s="18"/>
-      <c r="M32" s="24" t="str">
-        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:X32,1)*1), "")</f>
+      <c r="M32" s="24" t="str" cm="1">
+        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:Y32,1)*1), "")</f>
         <v/>
       </c>
       <c r="N32" s="8"/>
@@ -2321,8 +2389,8 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
+      <c r="X32" s="8"/>
+      <c r="Y32" s="8"/>
       <c r="AD32" s="6"/>
     </row>
     <row r="33" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2342,13 +2410,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K33" s="24" t="str">
-        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:X33,5,1)*1), "")</f>
+      <c r="K33" s="24" t="str" cm="1">
+        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:Y33,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L33" s="18"/>
-      <c r="M33" s="24" t="str">
-        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:X33,1)*1), "")</f>
+      <c r="M33" s="24" t="str" cm="1">
+        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:Y33,1)*1), "")</f>
         <v/>
       </c>
       <c r="N33" s="8"/>
@@ -2361,8 +2429,8 @@
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6"/>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="8"/>
       <c r="AD33" s="6"/>
     </row>
     <row r="34" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2382,13 +2450,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K34" s="24" t="str">
-        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:X34,5,1)*1), "")</f>
+      <c r="K34" s="24" t="str" cm="1">
+        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:Y34,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L34" s="18"/>
-      <c r="M34" s="24" t="str">
-        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:X34,1)*1), "")</f>
+      <c r="M34" s="24" t="str" cm="1">
+        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:Y34,1)*1), "")</f>
         <v/>
       </c>
       <c r="N34" s="8"/>
@@ -2401,8 +2469,8 @@
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="6"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="8"/>
       <c r="AD34" s="6"/>
     </row>
     <row r="35" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2422,13 +2490,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K35" s="24" t="str">
-        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:X35,5,1)*1), "")</f>
+      <c r="K35" s="24" t="str" cm="1">
+        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:Y35,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L35" s="18"/>
-      <c r="M35" s="24" t="str">
-        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:X35,1)*1), "")</f>
+      <c r="M35" s="24" t="str" cm="1">
+        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:Y35,1)*1), "")</f>
         <v/>
       </c>
       <c r="N35" s="8"/>
@@ -2441,8 +2509,8 @@
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="6"/>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="8"/>
       <c r="AD35" s="6"/>
     </row>
     <row r="36" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2462,13 +2530,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K36" s="24" t="str">
-        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:X36,5,1)*1), "")</f>
+      <c r="K36" s="24" t="str" cm="1">
+        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L36" s="18"/>
-      <c r="M36" s="24" t="str">
-        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:X36,1)*1), "")</f>
+      <c r="M36" s="24" t="str" cm="1">
+        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
         <v/>
       </c>
       <c r="N36" s="8"/>
@@ -2481,8 +2549,8 @@
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
+      <c r="X36" s="8"/>
+      <c r="Y36" s="8"/>
       <c r="AD36" s="6"/>
     </row>
     <row r="37" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2502,13 +2570,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="24" t="str">
-        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:X37,5,1)*1), "")</f>
+      <c r="K37" s="24" t="str" cm="1">
+        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:Y37,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L37" s="18"/>
-      <c r="M37" s="24" t="str">
-        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:X37,1)*1), "")</f>
+      <c r="M37" s="24" t="str" cm="1">
+        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:Y37,1)*1), "")</f>
         <v/>
       </c>
       <c r="N37" s="8"/>
@@ -2521,8 +2589,8 @@
       <c r="U37" s="8"/>
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
-      <c r="X37" s="6"/>
-      <c r="Y37" s="6"/>
+      <c r="X37" s="8"/>
+      <c r="Y37" s="8"/>
       <c r="AD37" s="6"/>
     </row>
     <row r="38" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2542,13 +2610,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K38" s="24" t="str">
-        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:X38,5,1)*1), "")</f>
+      <c r="K38" s="24" t="str" cm="1">
+        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:Y38,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L38" s="18"/>
-      <c r="M38" s="24" t="str">
-        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:X38,1)*1), "")</f>
+      <c r="M38" s="24" t="str" cm="1">
+        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:Y38,1)*1), "")</f>
         <v/>
       </c>
       <c r="N38" s="8"/>
@@ -2561,8 +2629,8 @@
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="6"/>
+      <c r="X38" s="8"/>
+      <c r="Y38" s="8"/>
       <c r="AD38" s="6"/>
     </row>
     <row r="39" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2582,13 +2650,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K39" s="24" t="str">
-        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:X39,5,1)*1), "")</f>
+      <c r="K39" s="24" t="str" cm="1">
+        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:Y39,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L39" s="18"/>
-      <c r="M39" s="24" t="str">
-        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:X39,1)*1), "")</f>
+      <c r="M39" s="24" t="str" cm="1">
+        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:Y39,1)*1), "")</f>
         <v/>
       </c>
       <c r="N39" s="8"/>
@@ -2601,8 +2669,8 @@
       <c r="U39" s="8"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="6"/>
+      <c r="X39" s="8"/>
+      <c r="Y39" s="8"/>
       <c r="AD39" s="6"/>
     </row>
     <row r="40" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2622,13 +2690,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K40" s="24" t="str">
-        <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:X40,5,1)*1), "")</f>
+      <c r="K40" s="24" t="str" cm="1">
+        <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:Y40,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L40" s="18"/>
-      <c r="M40" s="24" t="str">
-        <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:X40,1)*1), "")</f>
+      <c r="M40" s="24" t="str" cm="1">
+        <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:Y40,1)*1), "")</f>
         <v/>
       </c>
       <c r="N40" s="8"/>
@@ -2641,8 +2709,8 @@
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="6"/>
+      <c r="X40" s="8"/>
+      <c r="Y40" s="8"/>
       <c r="AD40" s="6"/>
     </row>
     <row r="41" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
@@ -2771,13 +2839,13 @@
         <v>9</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="N44" s="6"/>
       <c r="T44" s="6"/>
@@ -2794,7 +2862,7 @@
     </row>
     <row r="45" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" s="6">
         <v>1</v>
@@ -2806,10 +2874,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
@@ -2827,9 +2895,11 @@
         <v>0</v>
       </c>
       <c r="L45" s="6">
-        <v>0</v>
-      </c>
-      <c r="M45" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="M45" s="6">
+        <v>1</v>
+      </c>
       <c r="N45" s="27">
         <f t="shared" ref="N45:N48" si="4">SUM(B45:M45)</f>
         <v>9</v>
@@ -2860,10 +2930,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="6">
         <v>1</v>
@@ -2875,18 +2945,20 @@
         <v>1</v>
       </c>
       <c r="J46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="6">
         <v>0</v>
       </c>
       <c r="L46" s="6">
-        <v>0</v>
-      </c>
-      <c r="M46" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="M46" s="6">
+        <v>1</v>
+      </c>
       <c r="N46" s="27">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" s="6"/>
       <c r="U46" s="6"/>
@@ -2902,19 +2974,19 @@
     </row>
     <row r="47" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B47" s="6">
         <v>0</v>
       </c>
       <c r="C47" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" s="6">
         <v>0</v>
       </c>
       <c r="E47" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6">
         <v>0</v>
@@ -2923,24 +2995,26 @@
         <v>0</v>
       </c>
       <c r="H47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" s="6">
         <v>0</v>
       </c>
       <c r="L47" s="6">
-        <v>0</v>
-      </c>
-      <c r="M47" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="M47" s="6">
+        <v>2</v>
+      </c>
       <c r="N47" s="27">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -2956,16 +3030,16 @@
     </row>
     <row r="48" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" s="6">
         <v>0</v>
       </c>
       <c r="C48" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="6">
         <v>0</v>
@@ -2977,24 +3051,26 @@
         <v>0</v>
       </c>
       <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6">
+        <v>4</v>
+      </c>
+      <c r="J48" s="6">
         <v>1</v>
-      </c>
-      <c r="I48" s="6">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6">
-        <v>0</v>
       </c>
       <c r="K48" s="6">
         <v>0</v>
       </c>
       <c r="L48" s="6">
+        <v>1</v>
+      </c>
+      <c r="M48" s="6">
         <v>0</v>
       </c>
-      <c r="M48" s="6"/>
       <c r="N48" s="27">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
@@ -3016,19 +3092,19 @@
       </c>
       <c r="C49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,1,4,1</v>
       </c>
       <c r="D49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,1</v>
+        <v>1,1,0,2</v>
       </c>
       <c r="E49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="F49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="G49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3036,15 +3112,15 @@
       </c>
       <c r="H49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,1</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="I49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,1,1,4</v>
       </c>
       <c r="J49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,0,0,0</v>
+        <v>1,1,1,1</v>
       </c>
       <c r="K49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3052,11 +3128,11 @@
       </c>
       <c r="L49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0,0,0,0</v>
+        <v>1,1,1,1</v>
       </c>
       <c r="M49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>,,,</v>
+        <v>1,1,2,0</v>
       </c>
       <c r="N49" s="6"/>
       <c r="T49" s="6"/>
@@ -3202,40 +3278,40 @@
     <row r="54" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M54" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
@@ -33187,10 +33263,14 @@
         <v>9</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
@@ -33207,15 +33287,15 @@
       </c>
       <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="11">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="11">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="11">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
@@ -33227,26 +33307,32 @@
       </c>
       <c r="H2" s="11">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" s="11">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="11">
         <f t="array" ref="L2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>1</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
+      <c r="M2" s="11">
+        <f t="array" ref="M2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="11">
+        <f t="array" ref="N2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>1</v>
+      </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
@@ -33261,7 +33347,7 @@
       </c>
       <c r="C3" s="23">
         <f>C2/MatchesDB!$B$1</f>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D3" s="23">
         <f>D2/MatchesDB!$B$1</f>
@@ -33273,11 +33359,11 @@
       </c>
       <c r="F3" s="23">
         <f>F2/MatchesDB!$B$1</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G3" s="23">
         <f>G2/MatchesDB!$B$1</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H3" s="23">
         <f>H2/MatchesDB!$B$1</f>
@@ -33285,11 +33371,11 @@
       </c>
       <c r="I3" s="23">
         <f>I2/MatchesDB!$B$1</f>
-        <v>0.2</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J3" s="23">
         <f>J2/(MatchesDB!$B$1-4)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3" s="23">
         <f>K2/MatchesDB!$B$1</f>
@@ -33297,10 +33383,16 @@
       </c>
       <c r="L3" s="23">
         <f>L2/MatchesDB!$B$1</f>
-        <v>0.2</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M3" s="23">
+        <f>M2/MatchesDB!$B$1</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N3" s="23">
+        <f>N2/MatchesDB!$B$1</f>
+        <v>0.16666666666666666</v>
+      </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
@@ -33317,15 +33409,15 @@
       </c>
       <c r="C4" s="25">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="25">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="25">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="25">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33337,26 +33429,32 @@
       </c>
       <c r="H4" s="25">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="25">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="25">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="25">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="25">
         <f t="array" ref="L4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>1</v>
       </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="M4" s="25">
+        <f t="array" ref="M4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="25">
+        <f t="array" ref="N4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>1</v>
+      </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
@@ -33403,14 +33501,20 @@
       </c>
       <c r="K5" s="23">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L5" s="23">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="M5" s="23">
+        <f t="shared" ref="M5:N5" si="1">M4/M2</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -33431,7 +33535,7 @@
       </c>
       <c r="D6" s="11" cm="1">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" s="11">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33451,22 +33555,28 @@
       </c>
       <c r="I6" s="11">
         <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="11">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="11">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="11">
         <f t="array" ref="L6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="11">
+        <f t="array" ref="M6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
+        <f t="array" ref="N6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>2</v>
+      </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
@@ -33480,47 +33590,53 @@
         <v>38</v>
       </c>
       <c r="C7" s="26">
-        <f t="shared" ref="C7:L7" si="1">C6/C2</f>
+        <f t="shared" ref="C7:L7" si="2">C6/C2</f>
         <v>0</v>
       </c>
       <c r="D7" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="E7" s="26">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F7" s="26">
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="E7" s="26">
-        <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="F7" s="26">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
       <c r="G7" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="H7" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="26">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K7" s="26">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L7" s="26">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J7" s="26">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="K7" s="26">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="L7" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+      <c r="M7" s="26">
+        <f t="shared" ref="M7:N7" si="3">M6/M2</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="26">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
@@ -33541,11 +33657,11 @@
       </c>
       <c r="D8" s="25">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="25">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="25">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33561,22 +33677,28 @@
       </c>
       <c r="I8" s="25">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="25">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K8" s="25">
         <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="25">
         <f t="array" ref="L8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="M8" s="25">
+        <f t="array" ref="M8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="25">
+        <f t="array" ref="N8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
+        <v>0</v>
+      </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
@@ -33590,47 +33712,53 @@
         <v>38</v>
       </c>
       <c r="C9" s="26">
-        <f t="shared" ref="C9:L9" si="2">C8/C2</f>
+        <f t="shared" ref="C9:L9" si="4">C8/C2</f>
         <v>0</v>
       </c>
       <c r="D9" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E9" s="26">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="26">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E9" s="26">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="F9" s="26">
-        <f t="shared" si="2"/>
+      <c r="G9" s="26">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G9" s="26">
-        <f t="shared" si="2"/>
+      <c r="H9" s="26">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H9" s="26">
-        <f t="shared" si="2"/>
+      <c r="I9" s="26">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I9" s="26">
-        <f t="shared" si="2"/>
+      <c r="J9" s="26">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K9" s="26">
+        <f t="shared" si="4"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L9" s="26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="26">
+        <f t="shared" ref="M9:N9" si="5">M8/M2</f>
         <v>1</v>
       </c>
-      <c r="J9" s="26">
-        <f t="shared" si="2"/>
+      <c r="N9" s="26">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K9" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
@@ -33646,47 +33774,53 @@
         <v>11</v>
       </c>
       <c r="C10" s="11">
-        <f t="shared" ref="C10:L10" si="3">C6+C8</f>
+        <f t="shared" ref="C10:L10" si="6">C6+C8</f>
         <v>0</v>
       </c>
       <c r="D10" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E10" s="11">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="E10" s="11">
-        <f t="shared" si="3"/>
+      <c r="G10" s="11">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="11">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="K10" s="11">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="F10" s="11">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="G10" s="11">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="3"/>
+      <c r="L10" s="11">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I10" s="11">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="J10" s="11">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K10" s="11">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L10" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="M10" s="11">
+        <f t="shared" ref="M10:N10" si="7">M6+M8</f>
+        <v>2</v>
+      </c>
+      <c r="N10" s="11">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
@@ -33700,47 +33834,53 @@
         <v>38</v>
       </c>
       <c r="C11" s="26">
-        <f t="shared" ref="C11:L11" si="4">C10/C2</f>
+        <f t="shared" ref="C11:L11" si="8">C10/C2</f>
         <v>0</v>
       </c>
       <c r="D11" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E11" s="26">
+        <f t="shared" si="8"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F11" s="26">
+        <f t="shared" si="8"/>
         <v>0.6</v>
       </c>
-      <c r="E11" s="26">
-        <f t="shared" si="4"/>
-        <v>0.6</v>
-      </c>
-      <c r="F11" s="26">
-        <f t="shared" si="4"/>
-        <v>0.6</v>
-      </c>
       <c r="G11" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="H11" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I11" s="26">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>0.5</v>
       </c>
       <c r="J11" s="26">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
+        <f t="shared" si="8"/>
+        <v>1.1666666666666667</v>
       </c>
       <c r="K11" s="26">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
+        <f t="shared" si="8"/>
+        <v>0.5</v>
       </c>
       <c r="L11" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="M11" s="26">
+        <f t="shared" ref="M11:N11" si="9">M10/M2</f>
+        <v>2</v>
+      </c>
+      <c r="N11" s="26">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>

--- a/JO11-1/JO11-1_matchesDB.xlsx
+++ b/JO11-1/JO11-1_matchesDB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/PRV/RKAVIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80535FEB-1D3D-41D8-8882-ADFAFAEF6540}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77DB9DA2-D15E-462F-9DBC-8BABAA8EEE48}"/>
   <bookViews>
-    <workbookView xWindow="-11130" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchesDB" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="73">
   <si>
     <t>Matches</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>Gustav Mahlerlaan 2009, 1081 LB Amsterdam</t>
+  </si>
+  <si>
+    <t>1,1,2,1</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,3,0</t>
   </si>
 </sst>
 </file>
@@ -829,7 +838,7 @@
       </c>
       <c r="B1" s="5">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="7">
@@ -905,7 +914,7 @@
       </c>
       <c r="B3" s="10">
         <f>COUNTIF(J11:J40,"L")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1016,7 +1025,7 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1053,7 +1062,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1090,7 +1099,7 @@
       </c>
       <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1551,7 +1560,7 @@
       </c>
       <c r="AD14" s="6"/>
     </row>
-    <row r="15" spans="1:30" ht="28.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1740,29 +1749,55 @@
       </c>
       <c r="J17" s="17" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K17" s="24" t="str" cm="1">
+        <v>L</v>
+      </c>
+      <c r="K17" s="24" cm="1">
         <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:Y17,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L17" s="18"/>
-      <c r="M17" s="24" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="L17" s="18">
+        <v>10</v>
+      </c>
+      <c r="M17" s="24" cm="1">
         <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:Y17,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y17" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="AD17" s="6"/>
     </row>
     <row r="18" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1794,29 +1829,55 @@
       </c>
       <c r="J18" s="17" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K18" s="24" t="str" cm="1">
+        <v>L</v>
+      </c>
+      <c r="K18" s="24" cm="1">
         <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:Y18,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L18" s="18"/>
-      <c r="M18" s="24" t="str" cm="1">
+        <v>3</v>
+      </c>
+      <c r="L18" s="18">
+        <v>5</v>
+      </c>
+      <c r="M18" s="24" cm="1">
         <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y18" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="AD18" s="6"/>
     </row>
     <row r="19" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -2874,10 +2935,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
@@ -2902,7 +2963,7 @@
       </c>
       <c r="N45" s="27">
         <f t="shared" ref="N45:N48" si="4">SUM(B45:M45)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
@@ -2930,22 +2991,22 @@
         <v>1</v>
       </c>
       <c r="E46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="6">
         <v>1</v>
       </c>
       <c r="H46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6">
         <v>1</v>
       </c>
       <c r="J46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6">
         <v>0</v>
@@ -2954,11 +3015,11 @@
         <v>1</v>
       </c>
       <c r="M46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="27">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" s="6"/>
       <c r="U46" s="6"/>
@@ -2980,41 +3041,41 @@
         <v>0</v>
       </c>
       <c r="C47" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="6">
         <v>0</v>
       </c>
       <c r="F47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6">
         <v>1</v>
       </c>
       <c r="J47" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6">
         <v>0</v>
       </c>
       <c r="L47" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" s="27">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -3039,10 +3100,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6">
         <v>0</v>
@@ -3054,23 +3115,23 @@
         <v>0</v>
       </c>
       <c r="I48" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J48" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6">
         <v>0</v>
       </c>
       <c r="L48" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="6">
         <v>0</v>
       </c>
       <c r="N48" s="27">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
@@ -3092,19 +3153,19 @@
       </c>
       <c r="C49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,4,1</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="D49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,2</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="E49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0,0,0,0</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="F49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0,0,0,0</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="G49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3112,15 +3173,15 @@
       </c>
       <c r="H49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="I49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,4</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="J49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,1</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="K49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3128,11 +3189,11 @@
       </c>
       <c r="L49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,1</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="M49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,2,0</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="N49" s="6"/>
       <c r="T49" s="6"/>
@@ -3281,37 +3342,37 @@
         <v>46</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>46</v>
       </c>
       <c r="H54" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I54" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="J54" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>45</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
@@ -33287,39 +33348,39 @@
       </c>
       <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="11">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="11">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="11">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="11">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" s="11">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" s="11">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" s="11">
         <f t="array" ref="L2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
@@ -33327,11 +33388,11 @@
       </c>
       <c r="M2" s="11">
         <f t="array" ref="M2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" s="11">
         <f t="array" ref="N2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -33347,7 +33408,7 @@
       </c>
       <c r="C3" s="23">
         <f>C2/MatchesDB!$B$1</f>
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="D3" s="23">
         <f>D2/MatchesDB!$B$1</f>
@@ -33359,11 +33420,11 @@
       </c>
       <c r="F3" s="23">
         <f>F2/MatchesDB!$B$1</f>
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="G3" s="23">
         <f>G2/MatchesDB!$B$1</f>
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="H3" s="23">
         <f>H2/MatchesDB!$B$1</f>
@@ -33371,11 +33432,11 @@
       </c>
       <c r="I3" s="23">
         <f>I2/MatchesDB!$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="J3" s="23">
-        <f>J2/(MatchesDB!$B$1-4)</f>
-        <v>3</v>
+        <f>J2/(MatchesDB!$B$1)</f>
+        <v>1</v>
       </c>
       <c r="K3" s="23">
         <f>K2/MatchesDB!$B$1</f>
@@ -33383,15 +33444,15 @@
       </c>
       <c r="L3" s="23">
         <f>L2/MatchesDB!$B$1</f>
-        <v>0.16666666666666666</v>
+        <v>0.125</v>
       </c>
       <c r="M3" s="23">
         <f>M2/MatchesDB!$B$1</f>
-        <v>0.16666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="N3" s="23">
         <f>N2/MatchesDB!$B$1</f>
-        <v>0.16666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -33409,39 +33470,39 @@
       </c>
       <c r="C4" s="25">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="25">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" s="25">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" s="25">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="25">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" s="25">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" s="25">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="25">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="25">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="25">
         <f t="array" ref="L4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33449,7 +33510,7 @@
       </c>
       <c r="M4" s="25">
         <f t="array" ref="M4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" s="25">
         <f t="array" ref="N4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33481,7 +33542,7 @@
       </c>
       <c r="F5" s="23">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G5" s="23">
         <f t="shared" si="0"/>
@@ -33489,11 +33550,11 @@
       </c>
       <c r="H5" s="23">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="I5" s="23">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J5" s="23">
         <f t="shared" si="0"/>
@@ -33501,7 +33562,7 @@
       </c>
       <c r="K5" s="23">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="L5" s="23">
         <f t="shared" si="0"/>
@@ -33513,7 +33574,7 @@
       </c>
       <c r="N5" s="23">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
@@ -33535,11 +33596,11 @@
       </c>
       <c r="D6" s="11" cm="1">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="11">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="11">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33547,7 +33608,7 @@
       </c>
       <c r="G6" s="11">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="11">
         <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33559,7 +33620,7 @@
       </c>
       <c r="J6" s="11">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6" s="11">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33595,19 +33656,19 @@
       </c>
       <c r="D7" s="26">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
+        <v>1.125</v>
       </c>
       <c r="E7" s="26">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="26">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="G7" s="26">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H7" s="26">
         <f t="shared" si="2"/>
@@ -33615,15 +33676,15 @@
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J7" s="26">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="K7" s="26">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="L7" s="26">
         <f t="shared" si="2"/>
@@ -33631,11 +33692,11 @@
       </c>
       <c r="M7" s="26">
         <f t="shared" ref="M7:N7" si="3">M6/M2</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N7" s="26">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -33657,15 +33718,15 @@
       </c>
       <c r="D8" s="25">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="25">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="25">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="25">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33673,7 +33734,7 @@
       </c>
       <c r="H8" s="25">
         <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="25">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33717,7 +33778,7 @@
       </c>
       <c r="D9" s="26">
         <f t="shared" si="4"/>
-        <v>0.16666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="E9" s="26">
         <f t="shared" si="4"/>
@@ -33725,7 +33786,7 @@
       </c>
       <c r="F9" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="G9" s="26">
         <f t="shared" si="4"/>
@@ -33733,7 +33794,7 @@
       </c>
       <c r="H9" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I9" s="26">
         <f t="shared" si="4"/>
@@ -33741,11 +33802,11 @@
       </c>
       <c r="J9" s="26">
         <f t="shared" si="4"/>
-        <v>0.83333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="K9" s="26">
         <f t="shared" si="4"/>
-        <v>0.16666666666666666</v>
+        <v>0.125</v>
       </c>
       <c r="L9" s="26">
         <f t="shared" si="4"/>
@@ -33753,7 +33814,7 @@
       </c>
       <c r="M9" s="26">
         <f t="shared" ref="M9:N9" si="5">M8/M2</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N9" s="26">
         <f t="shared" si="5"/>
@@ -33779,23 +33840,23 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="11">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="11">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="6"/>
@@ -33803,7 +33864,7 @@
       </c>
       <c r="J10" s="11">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K10" s="11">
         <f t="shared" si="6"/>
@@ -33839,35 +33900,35 @@
       </c>
       <c r="D11" s="26">
         <f t="shared" si="8"/>
-        <v>1.3333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="E11" s="26">
         <f t="shared" si="8"/>
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="F11" s="26">
         <f t="shared" si="8"/>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G11" s="26">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H11" s="26">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I11" s="26">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J11" s="26">
         <f t="shared" si="8"/>
-        <v>1.1666666666666667</v>
+        <v>1.375</v>
       </c>
       <c r="K11" s="26">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" si="8"/>
@@ -33875,11 +33936,11 @@
       </c>
       <c r="M11" s="26">
         <f t="shared" ref="M11:N11" si="9">M10/M2</f>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N11" s="26">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>

--- a/JO11-1/JO11-1_matchesDB.xlsx
+++ b/JO11-1/JO11-1_matchesDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/PRV/RKAVIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77DB9DA2-D15E-462F-9DBC-8BABAA8EEE48}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{289A0958-DED7-4430-8611-3772B9B89540}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3465" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchesDB" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="85">
   <si>
     <t>Matches</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Noam</t>
   </si>
   <si>
-    <t>Oefenen</t>
-  </si>
-  <si>
     <t>1,1,4,1</t>
   </si>
   <si>
@@ -278,6 +275,45 @@
   </si>
   <si>
     <t>1,1,3,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>Oefen</t>
+  </si>
+  <si>
+    <t>2e 23</t>
+  </si>
+  <si>
+    <t>RODA'23 Rksv JO11-5</t>
+  </si>
+  <si>
+    <t>ASV Blauw-Wit JO11-3</t>
+  </si>
+  <si>
+    <t>ASV Arsenal JO11-2</t>
+  </si>
+  <si>
+    <t>Swift JO11-4</t>
+  </si>
+  <si>
+    <t>Buitenveldert JO11-4</t>
+  </si>
+  <si>
+    <t>Sporting Martinus JO11-1</t>
+  </si>
+  <si>
+    <t>Buitensingel 8, 1114 BE Duivendrecht</t>
+  </si>
+  <si>
+    <t>Sloterweg 1043K, 1066 CC Amsterdam</t>
+  </si>
+  <si>
+    <t>Olympiaplein 31, 1077 CL Amsterdam</t>
+  </si>
+  <si>
+    <t>Amsterdamseweg 247, 1182 GZ Amstelveen</t>
   </si>
 </sst>
 </file>
@@ -531,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -600,6 +636,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -838,7 +876,7 @@
       </c>
       <c r="B1" s="5">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="7">
@@ -914,7 +952,7 @@
       </c>
       <c r="B3" s="10">
         <f>COUNTIF(J11:J40,"L")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1025,7 +1063,7 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1062,7 +1100,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1099,7 +1137,7 @@
       </c>
       <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1560,7 +1598,7 @@
       </c>
       <c r="AD14" s="6"/>
     </row>
-    <row r="15" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1649,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D16" s="20">
         <v>46277</v>
@@ -1686,10 +1724,10 @@
         <v>46</v>
       </c>
       <c r="O16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>45</v>
@@ -1704,16 +1742,16 @@
         <v>48</v>
       </c>
       <c r="U16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="V16" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="V16" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="W16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y16" s="6" t="s">
         <v>49</v>
@@ -1742,7 +1780,7 @@
         <v>55</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>32</v>
@@ -1766,25 +1804,25 @@
         <v>46</v>
       </c>
       <c r="O17" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="R17" s="8" t="s">
         <v>46</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T17" s="8" t="s">
         <v>46</v>
       </c>
       <c r="U17" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V17" s="8" t="s">
         <v>46</v>
@@ -1909,44 +1947,84 @@
       </c>
       <c r="J19" s="17" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K19" s="24" t="str" cm="1">
+        <v>L</v>
+      </c>
+      <c r="K19" s="24" cm="1">
         <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L19" s="18"/>
-      <c r="M19" s="24" t="str" cm="1">
+        <v>2</v>
+      </c>
+      <c r="L19" s="18">
+        <v>5</v>
+      </c>
+      <c r="M19" s="24" cm="1">
         <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="T19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="W19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y19" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="AD19" s="6"/>
     </row>
     <row r="20" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="17" t="str">
+      <c r="A20" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="B20" s="18">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="30">
+        <v>46319</v>
+      </c>
+      <c r="E20" s="31">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="J20" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -1975,18 +2053,32 @@
       <c r="AD20" s="6"/>
     </row>
     <row r="21" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="str">
+      <c r="A21" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B21" s="18">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="30">
+        <v>46326</v>
+      </c>
+      <c r="E21" s="31">
+        <v>0.375</v>
+      </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="J21" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2015,18 +2107,32 @@
       <c r="AD21" s="6"/>
     </row>
     <row r="22" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="17" t="str">
+      <c r="A22" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B22" s="18">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="30">
+        <v>46333</v>
+      </c>
+      <c r="E22" s="31">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="J22" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2055,18 +2161,32 @@
       <c r="AD22" s="6"/>
     </row>
     <row r="23" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="str">
+      <c r="A23" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="B23" s="18">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="30">
+        <v>46340</v>
+      </c>
+      <c r="E23" s="31">
+        <v>0.44791666666666669</v>
+      </c>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="J23" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2095,18 +2215,32 @@
       <c r="AD23" s="6"/>
     </row>
     <row r="24" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="str">
+      <c r="A24" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B24" s="18">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="30">
+        <v>46347</v>
+      </c>
+      <c r="E24" s="31">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="J24" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2135,18 +2269,32 @@
       <c r="AD24" s="6"/>
     </row>
     <row r="25" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="str">
+      <c r="A25" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B25" s="18">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="30">
+        <v>46354</v>
+      </c>
+      <c r="E25" s="31">
+        <v>0.44791666666666669</v>
+      </c>
       <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="J25" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2175,18 +2323,32 @@
       <c r="AD25" s="6"/>
     </row>
     <row r="26" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="17" t="str">
+      <c r="A26" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B26" s="18">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="30">
+        <v>46361</v>
+      </c>
+      <c r="E26" s="31">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="J26" s="17" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2221,7 +2383,7 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -3044,19 +3206,19 @@
         <v>0</v>
       </c>
       <c r="D47" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="6">
         <v>0</v>
       </c>
       <c r="F47" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6">
         <v>1</v>
@@ -3075,7 +3237,7 @@
       </c>
       <c r="N47" s="27">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -3097,13 +3259,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="6">
+        <v>0</v>
+      </c>
+      <c r="D48" s="6">
         <v>1</v>
       </c>
-      <c r="D48" s="6">
+      <c r="E48" s="6">
         <v>0</v>
-      </c>
-      <c r="E48" s="6">
-        <v>1</v>
       </c>
       <c r="F48" s="6">
         <v>0</v>
@@ -3131,7 +3293,7 @@
       </c>
       <c r="N48" s="27">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
@@ -3153,19 +3315,19 @@
       </c>
       <c r="C49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,1</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="D49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="E49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,1</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="F49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="G49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3173,7 +3335,7 @@
       </c>
       <c r="H49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>1,0,0,0</v>
+        <v>1,0,1,0</v>
       </c>
       <c r="I49" s="6" t="str">
         <f t="shared" si="5"/>
@@ -3342,22 +3504,22 @@
         <v>46</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="E54" s="6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>46</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>48</v>
@@ -33340,7 +33502,7 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -33348,39 +33510,39 @@
       </c>
       <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="11">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="11">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="11">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="11">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="11">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="11">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="11">
         <f t="array" ref="L2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
@@ -33388,11 +33550,11 @@
       </c>
       <c r="M2" s="11">
         <f t="array" ref="M2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2" s="11">
         <f t="array" ref="N2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -33402,13 +33564,13 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="23">
         <f>C2/MatchesDB!$B$1</f>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="D3" s="23">
         <f>D2/MatchesDB!$B$1</f>
@@ -33420,11 +33582,11 @@
       </c>
       <c r="F3" s="23">
         <f>F2/MatchesDB!$B$1</f>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="G3" s="23">
         <f>G2/MatchesDB!$B$1</f>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="H3" s="23">
         <f>H2/MatchesDB!$B$1</f>
@@ -33432,7 +33594,7 @@
       </c>
       <c r="I3" s="23">
         <f>I2/MatchesDB!$B$1</f>
-        <v>0.5</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="J3" s="23">
         <f>J2/(MatchesDB!$B$1)</f>
@@ -33444,15 +33606,15 @@
       </c>
       <c r="L3" s="23">
         <f>L2/MatchesDB!$B$1</f>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="M3" s="23">
         <f>M2/MatchesDB!$B$1</f>
-        <v>0.375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="N3" s="23">
         <f>N2/MatchesDB!$B$1</f>
-        <v>0.375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -33462,7 +33624,7 @@
       <c r="T3" s="6"/>
     </row>
     <row r="4" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="32" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -33470,27 +33632,27 @@
       </c>
       <c r="C4" s="25">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="25">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="25">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="25">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="25">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="25">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="25">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33498,7 +33660,7 @@
       </c>
       <c r="J4" s="25">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="25">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33510,7 +33672,7 @@
       </c>
       <c r="M4" s="25">
         <f t="array" ref="M4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(M$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" s="25">
         <f t="array" ref="N4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(N$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33524,7 +33686,7 @@
       <c r="T4" s="6"/>
     </row>
     <row r="5" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="4" t="s">
         <v>33</v>
       </c>
@@ -33542,7 +33704,7 @@
       </c>
       <c r="F5" s="23">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="G5" s="23">
         <f t="shared" si="0"/>
@@ -33550,11 +33712,11 @@
       </c>
       <c r="H5" s="23">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="I5" s="23">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="J5" s="23">
         <f t="shared" si="0"/>
@@ -33562,7 +33724,7 @@
       </c>
       <c r="K5" s="23">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L5" s="23">
         <f t="shared" si="0"/>
@@ -33574,7 +33736,7 @@
       </c>
       <c r="N5" s="23">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
@@ -33584,7 +33746,7 @@
       <c r="T5" s="6"/>
     </row>
     <row r="6" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="32" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -33616,11 +33778,11 @@
       </c>
       <c r="I6" s="11">
         <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="11">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" s="11">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33646,7 +33808,7 @@
       <c r="T6" s="6"/>
     </row>
     <row r="7" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
@@ -33656,19 +33818,19 @@
       </c>
       <c r="D7" s="26">
         <f t="shared" si="2"/>
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="E7" s="26">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="F7" s="26">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.375</v>
       </c>
       <c r="G7" s="26">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="H7" s="26">
         <f t="shared" si="2"/>
@@ -33676,15 +33838,15 @@
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="J7" s="26">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="K7" s="26">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="L7" s="26">
         <f t="shared" si="2"/>
@@ -33692,11 +33854,11 @@
       </c>
       <c r="M7" s="26">
         <f t="shared" ref="M7:N7" si="3">M6/M2</f>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="N7" s="26">
         <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -33706,7 +33868,7 @@
       <c r="T7" s="6"/>
     </row>
     <row r="8" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="32" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -33722,7 +33884,7 @@
       </c>
       <c r="E8" s="25">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="25">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33768,7 +33930,7 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
@@ -33778,15 +33940,15 @@
       </c>
       <c r="D9" s="26">
         <f t="shared" si="4"/>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E9" s="26">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="F9" s="26">
         <f t="shared" si="4"/>
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="26">
         <f t="shared" si="4"/>
@@ -33794,7 +33956,7 @@
       </c>
       <c r="H9" s="26">
         <f t="shared" si="4"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I9" s="26">
         <f t="shared" si="4"/>
@@ -33802,11 +33964,11 @@
       </c>
       <c r="J9" s="26">
         <f t="shared" si="4"/>
-        <v>0.625</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="K9" s="26">
         <f t="shared" si="4"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="L9" s="26">
         <f t="shared" si="4"/>
@@ -33814,7 +33976,7 @@
       </c>
       <c r="M9" s="26">
         <f t="shared" ref="M9:N9" si="5">M8/M2</f>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="N9" s="26">
         <f t="shared" si="5"/>
@@ -33828,7 +33990,7 @@
       <c r="T9" s="6"/>
     </row>
     <row r="10" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="32" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -33844,7 +34006,7 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="6"/>
@@ -33860,11 +34022,11 @@
       </c>
       <c r="I10" s="11">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="11">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="11">
         <f t="shared" si="6"/>
@@ -33890,7 +34052,7 @@
       <c r="T10" s="6"/>
     </row>
     <row r="11" spans="1:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
@@ -33900,7 +34062,7 @@
       </c>
       <c r="D11" s="26">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="E11" s="26">
         <f t="shared" si="8"/>
@@ -33908,27 +34070,27 @@
       </c>
       <c r="F11" s="26">
         <f t="shared" si="8"/>
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="G11" s="26">
         <f t="shared" si="8"/>
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="26">
         <f t="shared" si="8"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I11" s="26">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="J11" s="26">
         <f t="shared" si="8"/>
-        <v>1.375</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="K11" s="26">
         <f t="shared" si="8"/>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" si="8"/>
@@ -33936,11 +34098,11 @@
       </c>
       <c r="M11" s="26">
         <f t="shared" ref="M11:N11" si="9">M10/M2</f>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="N11" s="26">
         <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
